--- a/Horarios/HorarioWAN_Ago2025.xlsx
+++ b/Horarios/HorarioWAN_Ago2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{8C644F6E-BB9D-4B58-9622-BDBA9672E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{257490FB-71D8-4150-B191-8795EF9B3FF9}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{8C644F6E-BB9D-4B58-9622-BDBA9672E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0EFF5F6-B9CD-49D9-A8DF-4DE8F4AF4761}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -528,16 +528,22 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -549,24 +555,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -576,10 +579,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,6 +602,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -947,13 +951,13 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1"/>
@@ -968,9 +972,9 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -979,13 +983,13 @@
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1"/>
@@ -996,9 +1000,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1027,13 +1031,13 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1"/>
@@ -1048,9 +1052,9 @@
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1059,13 +1063,13 @@
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="31" t="s">
+      <c r="C11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="1"/>
@@ -1076,9 +1080,9 @@
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="36"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1104,13 +1108,13 @@
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="1"/>
@@ -1121,9 +1125,9 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1132,11 +1136,11 @@
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="C17" s="39"/>
+      <c r="D17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="1"/>
@@ -1147,9 +1151,9 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1175,13 +1179,13 @@
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="35" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="1"/>
@@ -1196,9 +1200,9 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1207,13 +1211,13 @@
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="31" t="s">
+      <c r="C23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="1"/>
@@ -1224,9 +1228,9 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1251,13 +1255,13 @@
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="30" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="1"/>
@@ -1268,9 +1272,9 @@
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="29"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="1">
         <v>2</v>
       </c>
@@ -1285,13 +1289,13 @@
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="29"/>
+      <c r="C29" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="31"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1300,9 +1304,9 @@
       <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="30"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="32"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -1331,13 +1335,13 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="28" t="s">
+      <c r="C33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="30" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="1"/>
@@ -1348,9 +1352,9 @@
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="29"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="31"/>
       <c r="F34" s="1">
         <v>2</v>
       </c>
@@ -1365,13 +1369,13 @@
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="29"/>
+      <c r="E35" s="31"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1380,9 +1384,9 @@
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="30"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="32"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -1411,13 +1415,13 @@
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="24" t="s">
+      <c r="C39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="1"/>
@@ -1428,9 +1432,9 @@
       <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1439,13 +1443,13 @@
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="1"/>
@@ -1456,9 +1460,9 @@
       <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -1518,13 +1522,13 @@
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="24" t="s">
+      <c r="D45" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="1"/>
@@ -1541,9 +1545,9 @@
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
       <c r="F46" s="1">
         <v>2</v>
       </c>
@@ -1564,11 +1568,11 @@
       <c r="B47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="26" t="s">
+      <c r="C47" s="41"/>
+      <c r="D47" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="33" t="s">
+      <c r="E47" s="35" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="1"/>
@@ -1585,9 +1589,9 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="34"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="36"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -1627,13 +1631,13 @@
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="31" t="s">
+      <c r="D51" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>5</v>
       </c>
       <c r="F51" s="1">
@@ -1651,9 +1655,9 @@
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="31"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="37"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -1663,11 +1667,11 @@
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="26" t="s">
+      <c r="C53" s="41"/>
+      <c r="D53" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F53" s="1"/>
@@ -1678,9 +1682,9 @@
       <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -1727,13 +1731,13 @@
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="28" t="s">
+      <c r="C57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="28" t="s">
+      <c r="E57" s="30" t="s">
         <v>24</v>
       </c>
       <c r="F57" s="1"/>
@@ -1744,9 +1748,9 @@
       <c r="B58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="25"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
       <c r="F58" s="1">
         <v>4</v>
       </c>
@@ -1761,11 +1765,11 @@
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -1774,9 +1778,9 @@
       <c r="B60" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -1806,50 +1810,6 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C45:C48"/>
     <mergeCell ref="C57:C58"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="D57:D60"/>
@@ -1859,6 +1819,50 @@
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E27:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -1902,13 +1906,13 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1916,21 +1920,21 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1938,9 +1942,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
@@ -1960,13 +1964,13 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1974,21 +1978,21 @@
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="31" t="s">
+      <c r="C11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1996,9 +2000,9 @@
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="36"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="34"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
@@ -2015,13 +2019,13 @@
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="35" t="s">
+      <c r="C15" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="D15" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2029,19 +2033,21 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="C17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2049,9 +2055,9 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
@@ -2068,13 +2074,13 @@
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="35" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2082,21 +2088,21 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="31" t="s">
+      <c r="C23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2104,9 +2110,9 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="34"/>
     </row>
     <row r="26" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7" t="s">
@@ -2120,13 +2126,13 @@
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="30" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2134,29 +2140,27 @@
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="29"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="31"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="29"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="30"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="32"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
@@ -2176,13 +2180,13 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="28" t="s">
+      <c r="C33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="30" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2190,29 +2194,29 @@
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="29"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="31"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="29"/>
+      <c r="E35" s="31"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="30"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="32"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
@@ -2232,13 +2236,13 @@
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="24" t="s">
+      <c r="C39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2246,21 +2250,21 @@
       <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2268,9 +2272,9 @@
       <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
@@ -2290,13 +2294,13 @@
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="24" t="s">
+      <c r="D45" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2304,19 +2308,19 @@
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="26" t="s">
+      <c r="C47" s="41"/>
+      <c r="D47" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="33" t="s">
+      <c r="E47" s="35" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2324,9 +2328,9 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="34"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="36"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
@@ -2346,13 +2350,13 @@
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="31" t="s">
+      <c r="D51" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2360,19 +2364,19 @@
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="31"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="37"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="26" t="s">
+      <c r="C53" s="41"/>
+      <c r="D53" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2380,9 +2384,9 @@
       <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="5"/>
@@ -2402,13 +2406,13 @@
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D57" s="28" t="s">
+      <c r="D57" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="E57" s="28" t="s">
+      <c r="E57" s="30" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2416,25 +2420,25 @@
       <c r="B58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="5"/>
@@ -2444,6 +2448,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="E57:E60"/>
     <mergeCell ref="C41:C42"/>
@@ -2460,42 +2500,6 @@
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="73" orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_Ago2025.xlsx
+++ b/Horarios/HorarioWAN_Ago2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{8C644F6E-BB9D-4B58-9622-BDBA9672E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0EFF5F6-B9CD-49D9-A8DF-4DE8F4AF4761}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{8C644F6E-BB9D-4B58-9622-BDBA9672E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1088A6A4-014E-40AC-A680-04DAE51FDAAE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -269,7 +269,7 @@
     </r>
   </si>
   <si>
-    <t>ASSESSMENT</t>
+    <t>EVALUACIÓN DE ACTIVIDADES</t>
   </si>
 </sst>
 </file>
@@ -528,58 +528,58 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,10 +602,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -951,13 +947,13 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1"/>
@@ -972,9 +968,9 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -983,13 +979,13 @@
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="26" t="s">
+      <c r="D5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1"/>
@@ -1000,9 +996,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1031,13 +1027,13 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1"/>
@@ -1052,9 +1048,9 @@
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1063,13 +1059,13 @@
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="C11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="1"/>
@@ -1080,9 +1076,9 @@
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="34"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1108,13 +1104,13 @@
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="35" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="1"/>
@@ -1125,9 +1121,9 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1136,11 +1132,11 @@
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="26" t="s">
+      <c r="C17" s="38"/>
+      <c r="D17" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="1"/>
@@ -1151,9 +1147,9 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1179,13 +1175,13 @@
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="1"/>
@@ -1200,9 +1196,9 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="34"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1211,13 +1207,13 @@
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="37" t="s">
+      <c r="C23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="31" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="1"/>
@@ -1228,9 +1224,9 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="34"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="36"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1255,13 +1251,13 @@
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="28" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="1"/>
@@ -1272,9 +1268,9 @@
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="31"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="29"/>
       <c r="F28" s="1">
         <v>2</v>
       </c>
@@ -1289,13 +1285,13 @@
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="31"/>
+      <c r="C29" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="29"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1304,9 +1300,9 @@
       <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="32"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="30"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -1335,13 +1331,13 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="30" t="s">
+      <c r="C33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="28" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="1"/>
@@ -1352,9 +1348,9 @@
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="31"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="29"/>
       <c r="F34" s="1">
         <v>2</v>
       </c>
@@ -1369,13 +1365,13 @@
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="31"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1384,9 +1380,9 @@
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="32"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="30"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -1415,13 +1411,13 @@
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="26" t="s">
+      <c r="C39" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="1"/>
@@ -1432,9 +1428,9 @@
       <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1443,13 +1439,13 @@
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="26" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="1"/>
@@ -1460,9 +1456,9 @@
       <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -1522,13 +1518,13 @@
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="26" t="s">
+      <c r="D45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="1"/>
@@ -1545,9 +1541,9 @@
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="41"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
       <c r="F46" s="1">
         <v>2</v>
       </c>
@@ -1568,11 +1564,11 @@
       <c r="B47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="41"/>
-      <c r="D47" s="24" t="s">
+      <c r="C47" s="32"/>
+      <c r="D47" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="35" t="s">
+      <c r="E47" s="33" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="1"/>
@@ -1589,9 +1585,9 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="36"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="34"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -1631,13 +1627,13 @@
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="30" t="s">
+      <c r="C51" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="37" t="s">
+      <c r="D51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="31" t="s">
         <v>5</v>
       </c>
       <c r="F51" s="1">
@@ -1655,9 +1651,9 @@
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="37"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="31"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -1667,11 +1663,11 @@
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="41"/>
-      <c r="D53" s="24" t="s">
+      <c r="C53" s="32"/>
+      <c r="D53" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="26" t="s">
         <v>11</v>
       </c>
       <c r="F53" s="1"/>
@@ -1682,9 +1678,9 @@
       <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -1731,13 +1727,13 @@
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="30" t="s">
+      <c r="C57" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="30" t="s">
+      <c r="E57" s="28" t="s">
         <v>24</v>
       </c>
       <c r="F57" s="1"/>
@@ -1748,9 +1744,9 @@
       <c r="B58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
       <c r="F58" s="1">
         <v>4</v>
       </c>
@@ -1765,11 +1761,11 @@
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -1778,9 +1774,9 @@
       <c r="B60" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="25"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -1810,6 +1806,50 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C45:C48"/>
     <mergeCell ref="C57:C58"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="D57:D60"/>
@@ -1819,50 +1859,6 @@
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E27:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -1906,13 +1902,13 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="35" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1920,21 +1916,21 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="26" t="s">
+      <c r="D5" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1942,9 +1938,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
@@ -1964,13 +1960,13 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="35" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1978,21 +1974,21 @@
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="C11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="31" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2000,9 +1996,9 @@
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="34"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="36"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
@@ -2019,13 +2015,13 @@
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="35" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2033,21 +2029,21 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="26" t="s">
+      <c r="C17" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2055,9 +2051,9 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
@@ -2074,13 +2070,13 @@
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="33" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2088,21 +2084,21 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="34"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="37" t="s">
+      <c r="C23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="31" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2110,9 +2106,9 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="34"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="36"/>
     </row>
     <row r="26" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7" t="s">
@@ -2126,13 +2122,13 @@
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="28" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2140,27 +2136,27 @@
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="31"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="29"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="31"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="29"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="32"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="30"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
@@ -2180,13 +2176,13 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="30" t="s">
+      <c r="C33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="28" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2194,29 +2190,29 @@
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="31"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="29"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="31"/>
+      <c r="E35" s="29"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="32"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="30"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
@@ -2236,13 +2232,13 @@
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="26" t="s">
+      <c r="C39" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2250,21 +2246,21 @@
       <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="26" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2272,9 +2268,9 @@
       <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
@@ -2294,13 +2290,13 @@
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="26" t="s">
+      <c r="D45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2308,19 +2304,19 @@
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="41"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="41"/>
-      <c r="D47" s="24" t="s">
+      <c r="C47" s="32"/>
+      <c r="D47" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="35" t="s">
+      <c r="E47" s="33" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2328,9 +2324,9 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="36"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="34"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
@@ -2350,13 +2346,13 @@
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="30" t="s">
+      <c r="C51" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="37" t="s">
+      <c r="D51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="31" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2364,19 +2360,19 @@
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="37"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="31"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="41"/>
-      <c r="D53" s="24" t="s">
+      <c r="C53" s="32"/>
+      <c r="D53" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="26" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2384,9 +2380,9 @@
       <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="5"/>
@@ -2406,13 +2402,13 @@
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="30" t="s">
+      <c r="C57" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D57" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E57" s="30" t="s">
+      <c r="E57" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2420,25 +2416,25 @@
       <c r="B58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="5"/>
@@ -2448,11 +2444,37 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D57:D60"/>
+    <mergeCell ref="E57:E60"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -2469,37 +2491,11 @@
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D57:D60"/>
-    <mergeCell ref="E57:E60"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="73" orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_Ago2025.xlsx
+++ b/Horarios/HorarioWAN_Ago2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{8C644F6E-BB9D-4B58-9622-BDBA9672E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1088A6A4-014E-40AC-A680-04DAE51FDAAE}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{8C644F6E-BB9D-4B58-9622-BDBA9672E72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111F84A9-98D9-4086-96E7-51CECF59545C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_301" sheetId="2" r:id="rId1"/>
@@ -528,16 +528,22 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -549,24 +555,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -576,10 +579,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,6 +602,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -947,13 +951,13 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1"/>
@@ -968,9 +972,9 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -979,13 +983,13 @@
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1"/>
@@ -996,9 +1000,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1027,13 +1031,13 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1"/>
@@ -1048,9 +1052,9 @@
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1059,13 +1063,13 @@
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="31" t="s">
+      <c r="C11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="1"/>
@@ -1076,9 +1080,9 @@
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="36"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1104,13 +1108,13 @@
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="1"/>
@@ -1121,9 +1125,9 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1132,11 +1136,11 @@
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="C17" s="39"/>
+      <c r="D17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="1"/>
@@ -1147,9 +1151,9 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1175,13 +1179,13 @@
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="35" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="1"/>
@@ -1196,9 +1200,9 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="36"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1207,13 +1211,13 @@
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="31" t="s">
+      <c r="C23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>5</v>
       </c>
       <c r="F23" s="1"/>
@@ -1224,9 +1228,9 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1251,13 +1255,13 @@
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="30" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="1"/>
@@ -1268,9 +1272,9 @@
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="29"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="1">
         <v>2</v>
       </c>
@@ -1285,13 +1289,13 @@
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="29"/>
+      <c r="C29" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="31"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -1300,9 +1304,9 @@
       <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="30"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="32"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -1331,13 +1335,13 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="28" t="s">
+      <c r="C33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="30" t="s">
         <v>5</v>
       </c>
       <c r="F33" s="1"/>
@@ -1348,9 +1352,9 @@
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="29"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="31"/>
       <c r="F34" s="1">
         <v>2</v>
       </c>
@@ -1365,13 +1369,13 @@
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="29"/>
+      <c r="E35" s="31"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -1380,9 +1384,9 @@
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="30"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="32"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -1411,13 +1415,13 @@
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="24" t="s">
+      <c r="C39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="1"/>
@@ -1428,9 +1432,9 @@
       <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -1439,13 +1443,13 @@
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F41" s="1"/>
@@ -1456,9 +1460,9 @@
       <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -1518,13 +1522,13 @@
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="24" t="s">
+      <c r="D45" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="1"/>
@@ -1541,9 +1545,9 @@
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
       <c r="F46" s="1">
         <v>2</v>
       </c>
@@ -1564,11 +1568,11 @@
       <c r="B47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="26" t="s">
+      <c r="C47" s="41"/>
+      <c r="D47" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="33" t="s">
+      <c r="E47" s="35" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="1"/>
@@ -1585,9 +1589,9 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="34"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="36"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -1627,13 +1631,13 @@
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="31" t="s">
+      <c r="D51" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>5</v>
       </c>
       <c r="F51" s="1">
@@ -1651,9 +1655,9 @@
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="31"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="37"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -1663,11 +1667,11 @@
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="26" t="s">
+      <c r="C53" s="41"/>
+      <c r="D53" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="24" t="s">
         <v>11</v>
       </c>
       <c r="F53" s="1"/>
@@ -1678,9 +1682,9 @@
       <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -1727,13 +1731,13 @@
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="28" t="s">
+      <c r="C57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="28" t="s">
+      <c r="E57" s="30" t="s">
         <v>24</v>
       </c>
       <c r="F57" s="1"/>
@@ -1744,9 +1748,9 @@
       <c r="B58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="25"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
       <c r="F58" s="1">
         <v>4</v>
       </c>
@@ -1761,11 +1765,11 @@
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -1774,9 +1778,9 @@
       <c r="B60" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="27"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -1806,50 +1810,6 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C45:C48"/>
     <mergeCell ref="C57:C58"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="D57:D60"/>
@@ -1859,6 +1819,50 @@
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
     <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E27:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -1902,13 +1906,13 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1916,21 +1920,21 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1938,9 +1942,9 @@
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
@@ -1960,13 +1964,13 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1974,21 +1978,21 @@
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="31" t="s">
+      <c r="C11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1996,9 +2000,9 @@
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="36"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="34"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
@@ -2015,13 +2019,13 @@
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="33" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2029,21 +2033,21 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="C17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2051,9 +2055,9 @@
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
@@ -2070,13 +2074,13 @@
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="35" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2084,21 +2088,21 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="31" t="s">
+      <c r="C23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2106,9 +2110,9 @@
       <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="34"/>
     </row>
     <row r="26" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7" t="s">
@@ -2122,13 +2126,13 @@
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="30" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2136,27 +2140,27 @@
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="29"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="31"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="29"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="30"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="32"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
@@ -2176,13 +2180,13 @@
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="28" t="s">
+      <c r="C33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="30" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2190,29 +2194,29 @@
       <c r="B34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="29"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="31"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="29"/>
+      <c r="E35" s="31"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="30"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="32"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
@@ -2232,13 +2236,13 @@
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="24" t="s">
+      <c r="C39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2246,21 +2250,21 @@
       <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2268,9 +2272,9 @@
       <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
@@ -2290,13 +2294,13 @@
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="24" t="s">
+      <c r="D45" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2304,19 +2308,19 @@
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="32"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="32"/>
-      <c r="D47" s="26" t="s">
+      <c r="C47" s="41"/>
+      <c r="D47" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E47" s="33" t="s">
+      <c r="E47" s="35" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2324,9 +2328,9 @@
       <c r="B48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="34"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="36"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
@@ -2346,13 +2350,13 @@
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="C51" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="31" t="s">
+      <c r="D51" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="37" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2360,19 +2364,19 @@
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="31"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="37"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="26" t="s">
+      <c r="C53" s="41"/>
+      <c r="D53" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="E53" s="24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2380,9 +2384,9 @@
       <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="5"/>
@@ -2402,13 +2406,13 @@
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D57" s="28" t="s">
+      <c r="D57" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="E57" s="28" t="s">
+      <c r="E57" s="30" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2416,25 +2420,25 @@
       <c r="B58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61" s="5"/>
@@ -2444,6 +2448,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="E57:E60"/>
     <mergeCell ref="C41:C42"/>
@@ -2460,44 +2500,8 @@
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="73" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>